--- a/project_it215/tests/test_case_template_excel.xlsx
+++ b/project_it215/tests/test_case_template_excel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lemin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e3cf02ac30cf0a3/Documents/FastAPI/project_it215/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B737E0E4-BC1C-4EA4-87BA-04D25580637A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B737E0E4-BC1C-4EA4-87BA-04D25580637A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15B6DB84-E269-4C64-B5BE-64DA94BD0114}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="451">
   <si>
     <t>TEST CASE TEMPLATE</t>
   </si>
@@ -1357,36 +1357,6 @@
     <t>SYS-06</t>
   </si>
   <si>
-    <t>Gửi request với HTTP Method không hỗ trợ.</t>
-  </si>
-  <si>
-    <t>Gửi PUT /campaigns/1 (hệ thống chỉ hỗ trợ PATCH).</t>
-  </si>
-  <si>
-    <t>Method: PUT, URL: /campaigns/1</t>
-  </si>
-  <si>
-    <t>405 Method Not Allowed.</t>
-  </si>
-  <si>
-    <t>SYS-07</t>
-  </si>
-  <si>
-    <t>Gửi request với JSON body sai cú pháp (malformed JSON).</t>
-  </si>
-  <si>
-    <t>Gửi POST /campaigns với Body không đóng ngoặc nhọn.</t>
-  </si>
-  <si>
-    <t>Body: {"name": "Test"</t>
-  </si>
-  <si>
-    <t>422 Unprocessable Entity; Báo lỗi cú pháp JSON.</t>
-  </si>
-  <si>
-    <t>SYS-08</t>
-  </si>
-  <si>
     <t>Hệ thống gặp lỗi HTTPException tùy chỉnh.</t>
   </si>
   <si>
@@ -1394,33 +1364,6 @@
   </si>
   <si>
     <t>Định dạng JSON trả về đúng chuẩn custom_http_exception_handle: {"success": false, "status_code": , "error_detail": ""}.</t>
-  </si>
-  <si>
-    <t>SYS-09</t>
-  </si>
-  <si>
-    <t>Kiểm tra tính an toàn SQL Injection trong tìm kiếm.</t>
-  </si>
-  <si>
-    <t>Gửi GET /campaigns?name=' OR '1'='1.</t>
-  </si>
-  <si>
-    <t>Query: name=' OR '1'='1</t>
-  </si>
-  <si>
-    <t>200 OK; Xử lý an toàn qua ORM Parameterized Query, chỉ tìm các campaign có tên chứa đúng chuỗi đó.</t>
-  </si>
-  <si>
-    <t>SYS-10</t>
-  </si>
-  <si>
-    <t>Kiểm tra lưu trữ an toàn mật khẩu người dùng.</t>
-  </si>
-  <si>
-    <t>Đăng ký tài khoản và kiểm tra trực tiếp trường password_hash trong CSDL MySQL.</t>
-  </si>
-  <si>
-    <t>Mật khẩu được mã hóa an toàn bằng thuật toán bcrypt (bắt đầu bằng $2b$), không lưu trữ plain text.</t>
   </si>
   <si>
     <t>Marketing Campaign Management API</t>
@@ -1439,7 +1382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1521,6 +1464,11 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1954,7 +1902,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AC1004"/>
+  <dimension ref="A1:AC1000"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -2072,14 +2020,14 @@
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -2148,7 +2096,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="7" t="s">
@@ -2185,7 +2133,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="7" t="s">
@@ -2333,7 +2281,7 @@
       <c r="AB10" s="18"/>
       <c r="AC10" s="18"/>
     </row>
-    <row r="11" spans="1:29" ht="77.25" thickBot="1">
+    <row r="11" spans="1:29" ht="51.75" thickBot="1">
       <c r="A11" s="6"/>
       <c r="B11" s="23" t="s">
         <v>22</v>
@@ -2376,7 +2324,7 @@
       <c r="AB11" s="5"/>
       <c r="AC11" s="5"/>
     </row>
-    <row r="12" spans="1:29" ht="77.25" thickBot="1">
+    <row r="12" spans="1:29" ht="39" thickBot="1">
       <c r="A12" s="6"/>
       <c r="B12" s="23" t="s">
         <v>28</v>
@@ -2419,7 +2367,7 @@
       <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
     </row>
-    <row r="13" spans="1:29" ht="64.5" thickBot="1">
+    <row r="13" spans="1:29" ht="39" thickBot="1">
       <c r="A13" s="6"/>
       <c r="B13" s="23" t="s">
         <v>33</v>
@@ -2462,7 +2410,7 @@
       <c r="AB13" s="5"/>
       <c r="AC13" s="5"/>
     </row>
-    <row r="14" spans="1:29" ht="64.5" thickBot="1">
+    <row r="14" spans="1:29" ht="39" thickBot="1">
       <c r="A14" s="6"/>
       <c r="B14" s="23" t="s">
         <v>38</v>
@@ -2505,7 +2453,7 @@
       <c r="AB14" s="21"/>
       <c r="AC14" s="21"/>
     </row>
-    <row r="15" spans="1:29" ht="64.5" thickBot="1">
+    <row r="15" spans="1:29" ht="51.75" thickBot="1">
       <c r="A15" s="6"/>
       <c r="B15" s="23" t="s">
         <v>41</v>
@@ -2548,7 +2496,7 @@
       <c r="AB15" s="5"/>
       <c r="AC15" s="5"/>
     </row>
-    <row r="16" spans="1:29" ht="64.5" thickBot="1">
+    <row r="16" spans="1:29" ht="51.75" thickBot="1">
       <c r="A16" s="6"/>
       <c r="B16" s="23" t="s">
         <v>45</v>
@@ -2591,7 +2539,7 @@
       <c r="AB16" s="5"/>
       <c r="AC16" s="5"/>
     </row>
-    <row r="17" spans="1:29" ht="77.25" thickBot="1">
+    <row r="17" spans="1:29" ht="51.75" thickBot="1">
       <c r="A17" s="6"/>
       <c r="B17" s="23" t="s">
         <v>49</v>
@@ -2634,7 +2582,7 @@
       <c r="AB17" s="5"/>
       <c r="AC17" s="5"/>
     </row>
-    <row r="18" spans="1:29" ht="77.25" thickBot="1">
+    <row r="18" spans="1:29" ht="51.75" thickBot="1">
       <c r="A18" s="6"/>
       <c r="B18" s="23" t="s">
         <v>52</v>
@@ -2677,7 +2625,7 @@
       <c r="AB18" s="5"/>
       <c r="AC18" s="5"/>
     </row>
-    <row r="19" spans="1:29" ht="64.5" thickBot="1">
+    <row r="19" spans="1:29" ht="51.75" thickBot="1">
       <c r="A19" s="6"/>
       <c r="B19" s="23" t="s">
         <v>56</v>
@@ -2720,7 +2668,7 @@
       <c r="AB19" s="5"/>
       <c r="AC19" s="5"/>
     </row>
-    <row r="20" spans="1:29" ht="77.25" thickBot="1">
+    <row r="20" spans="1:29" ht="51.75" thickBot="1">
       <c r="A20" s="1"/>
       <c r="B20" s="23" t="s">
         <v>60</v>
@@ -2763,7 +2711,7 @@
       <c r="AB20" s="5"/>
       <c r="AC20" s="5"/>
     </row>
-    <row r="21" spans="1:29" ht="64.5" thickBot="1">
+    <row r="21" spans="1:29" ht="39" thickBot="1">
       <c r="A21" s="1"/>
       <c r="B21" s="23" t="s">
         <v>64</v>
@@ -2806,7 +2754,7 @@
       <c r="AB21" s="5"/>
       <c r="AC21" s="5"/>
     </row>
-    <row r="22" spans="1:29" ht="51.75" thickBot="1">
+    <row r="22" spans="1:29" ht="39" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="23" t="s">
         <v>69</v>
@@ -2849,7 +2797,7 @@
       <c r="AB22" s="5"/>
       <c r="AC22" s="5"/>
     </row>
-    <row r="23" spans="1:29" ht="51.75" thickBot="1">
+    <row r="23" spans="1:29" ht="26.25" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="23" t="s">
         <v>74</v>
@@ -2892,7 +2840,7 @@
       <c r="AB23" s="5"/>
       <c r="AC23" s="5"/>
     </row>
-    <row r="24" spans="1:29" ht="51.75" thickBot="1">
+    <row r="24" spans="1:29" ht="39" thickBot="1">
       <c r="A24" s="1"/>
       <c r="B24" s="23" t="s">
         <v>78</v>
@@ -2935,7 +2883,7 @@
       <c r="AB24" s="5"/>
       <c r="AC24" s="5"/>
     </row>
-    <row r="25" spans="1:29" ht="64.5" thickBot="1">
+    <row r="25" spans="1:29" ht="39" thickBot="1">
       <c r="A25" s="1"/>
       <c r="B25" s="23" t="s">
         <v>83</v>
@@ -2978,7 +2926,7 @@
       <c r="AB25" s="5"/>
       <c r="AC25" s="5"/>
     </row>
-    <row r="26" spans="1:29" ht="64.5" thickBot="1">
+    <row r="26" spans="1:29" ht="39" thickBot="1">
       <c r="A26" s="1"/>
       <c r="B26" s="23" t="s">
         <v>87</v>
@@ -3021,7 +2969,7 @@
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
     </row>
-    <row r="27" spans="1:29" ht="64.5" thickBot="1">
+    <row r="27" spans="1:29" ht="39" thickBot="1">
       <c r="A27" s="1"/>
       <c r="B27" s="23" t="s">
         <v>92</v>
@@ -3064,7 +3012,7 @@
       <c r="AB27" s="5"/>
       <c r="AC27" s="5"/>
     </row>
-    <row r="28" spans="1:29" ht="51.75" thickBot="1">
+    <row r="28" spans="1:29" ht="26.25" thickBot="1">
       <c r="A28" s="1"/>
       <c r="B28" s="23" t="s">
         <v>97</v>
@@ -3107,7 +3055,7 @@
       <c r="AB28" s="5"/>
       <c r="AC28" s="5"/>
     </row>
-    <row r="29" spans="1:29" ht="51.75" thickBot="1">
+    <row r="29" spans="1:29" ht="26.25" thickBot="1">
       <c r="A29" s="1"/>
       <c r="B29" s="23" t="s">
         <v>101</v>
@@ -3150,7 +3098,7 @@
       <c r="AB29" s="5"/>
       <c r="AC29" s="5"/>
     </row>
-    <row r="30" spans="1:29" ht="51.75" thickBot="1">
+    <row r="30" spans="1:29" ht="39" thickBot="1">
       <c r="A30" s="1"/>
       <c r="B30" s="23" t="s">
         <v>105</v>
@@ -3193,7 +3141,7 @@
       <c r="AB30" s="21"/>
       <c r="AC30" s="21"/>
     </row>
-    <row r="31" spans="1:29" ht="51.75" thickBot="1">
+    <row r="31" spans="1:29" ht="26.25" thickBot="1">
       <c r="A31" s="1"/>
       <c r="B31" s="23" t="s">
         <v>110</v>
@@ -3236,7 +3184,7 @@
       <c r="AB31" s="21"/>
       <c r="AC31" s="21"/>
     </row>
-    <row r="32" spans="1:29" ht="64.5" thickBot="1">
+    <row r="32" spans="1:29" ht="39" thickBot="1">
       <c r="A32" s="1"/>
       <c r="B32" s="23" t="s">
         <v>115</v>
@@ -3279,7 +3227,7 @@
       <c r="AB32" s="21"/>
       <c r="AC32" s="21"/>
     </row>
-    <row r="33" spans="1:29" ht="64.5" thickBot="1">
+    <row r="33" spans="1:29" ht="51.75" thickBot="1">
       <c r="A33" s="1"/>
       <c r="B33" s="23" t="s">
         <v>120</v>
@@ -3322,7 +3270,7 @@
       <c r="AB33" s="5"/>
       <c r="AC33" s="5"/>
     </row>
-    <row r="34" spans="1:29" ht="128.25" thickBot="1">
+    <row r="34" spans="1:29" ht="77.25" thickBot="1">
       <c r="A34" s="1"/>
       <c r="B34" s="23" t="s">
         <v>125</v>
@@ -3365,7 +3313,7 @@
       <c r="AB34" s="5"/>
       <c r="AC34" s="5"/>
     </row>
-    <row r="35" spans="1:29" ht="64.5" thickBot="1">
+    <row r="35" spans="1:29" ht="39" thickBot="1">
       <c r="A35" s="1"/>
       <c r="B35" s="23" t="s">
         <v>130</v>
@@ -3408,7 +3356,7 @@
       <c r="AB35" s="5"/>
       <c r="AC35" s="5"/>
     </row>
-    <row r="36" spans="1:29" ht="64.5" thickBot="1">
+    <row r="36" spans="1:29" ht="26.25" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="23" t="s">
         <v>134</v>
@@ -3451,7 +3399,7 @@
       <c r="AB36" s="5"/>
       <c r="AC36" s="5"/>
     </row>
-    <row r="37" spans="1:29" ht="64.5" thickBot="1">
+    <row r="37" spans="1:29" ht="39" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="23" t="s">
         <v>138</v>
@@ -3494,7 +3442,7 @@
       <c r="AB37" s="5"/>
       <c r="AC37" s="5"/>
     </row>
-    <row r="38" spans="1:29" ht="64.5" thickBot="1">
+    <row r="38" spans="1:29" ht="39" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="23" t="s">
         <v>142</v>
@@ -3537,7 +3485,7 @@
       <c r="AB38" s="5"/>
       <c r="AC38" s="5"/>
     </row>
-    <row r="39" spans="1:29" ht="64.5" thickBot="1">
+    <row r="39" spans="1:29" ht="51.75" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="23" t="s">
         <v>146</v>
@@ -3580,7 +3528,7 @@
       <c r="AB39" s="5"/>
       <c r="AC39" s="5"/>
     </row>
-    <row r="40" spans="1:29" ht="51.75" thickBot="1">
+    <row r="40" spans="1:29" ht="39" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="23" t="s">
         <v>151</v>
@@ -3623,7 +3571,7 @@
       <c r="AB40" s="5"/>
       <c r="AC40" s="5"/>
     </row>
-    <row r="41" spans="1:29" ht="51.75" thickBot="1">
+    <row r="41" spans="1:29" ht="39" thickBot="1">
       <c r="A41" s="1"/>
       <c r="B41" s="23" t="s">
         <v>156</v>
@@ -3666,7 +3614,7 @@
       <c r="AB41" s="5"/>
       <c r="AC41" s="5"/>
     </row>
-    <row r="42" spans="1:29" ht="51.75" thickBot="1">
+    <row r="42" spans="1:29" ht="26.25" thickBot="1">
       <c r="A42" s="1"/>
       <c r="B42" s="23" t="s">
         <v>161</v>
@@ -3709,7 +3657,7 @@
       <c r="AB42" s="5"/>
       <c r="AC42" s="5"/>
     </row>
-    <row r="43" spans="1:29" ht="51.75" thickBot="1">
+    <row r="43" spans="1:29" ht="26.25" thickBot="1">
       <c r="A43" s="1"/>
       <c r="B43" s="23" t="s">
         <v>166</v>
@@ -3752,7 +3700,7 @@
       <c r="AB43" s="5"/>
       <c r="AC43" s="5"/>
     </row>
-    <row r="44" spans="1:29" ht="64.5" thickBot="1">
+    <row r="44" spans="1:29" ht="39" thickBot="1">
       <c r="A44" s="1"/>
       <c r="B44" s="23" t="s">
         <v>171</v>
@@ -3795,7 +3743,7 @@
       <c r="AB44" s="5"/>
       <c r="AC44" s="5"/>
     </row>
-    <row r="45" spans="1:29" ht="64.5" thickBot="1">
+    <row r="45" spans="1:29" ht="39" thickBot="1">
       <c r="A45" s="1"/>
       <c r="B45" s="23" t="s">
         <v>176</v>
@@ -3838,7 +3786,7 @@
       <c r="AB45" s="5"/>
       <c r="AC45" s="5"/>
     </row>
-    <row r="46" spans="1:29" ht="64.5" thickBot="1">
+    <row r="46" spans="1:29" ht="39" thickBot="1">
       <c r="A46" s="1"/>
       <c r="B46" s="23" t="s">
         <v>180</v>
@@ -3881,7 +3829,7 @@
       <c r="AB46" s="5"/>
       <c r="AC46" s="5"/>
     </row>
-    <row r="47" spans="1:29" ht="102.75" thickBot="1">
+    <row r="47" spans="1:29" ht="51.75" thickBot="1">
       <c r="A47" s="1"/>
       <c r="B47" s="23" t="s">
         <v>185</v>
@@ -3924,7 +3872,7 @@
       <c r="AB47" s="5"/>
       <c r="AC47" s="5"/>
     </row>
-    <row r="48" spans="1:29" ht="64.5" thickBot="1">
+    <row r="48" spans="1:29" ht="39" thickBot="1">
       <c r="A48" s="1"/>
       <c r="B48" s="23" t="s">
         <v>190</v>
@@ -3967,7 +3915,7 @@
       <c r="AB48" s="5"/>
       <c r="AC48" s="5"/>
     </row>
-    <row r="49" spans="1:29" ht="51.75" thickBot="1">
+    <row r="49" spans="1:29" ht="26.25" thickBot="1">
       <c r="A49" s="1"/>
       <c r="B49" s="23" t="s">
         <v>194</v>
@@ -4010,7 +3958,7 @@
       <c r="AB49" s="5"/>
       <c r="AC49" s="5"/>
     </row>
-    <row r="50" spans="1:29" ht="64.5" thickBot="1">
+    <row r="50" spans="1:29" ht="39" thickBot="1">
       <c r="A50" s="1"/>
       <c r="B50" s="23" t="s">
         <v>198</v>
@@ -4053,7 +4001,7 @@
       <c r="AB50" s="5"/>
       <c r="AC50" s="5"/>
     </row>
-    <row r="51" spans="1:29" ht="51.75" thickBot="1">
+    <row r="51" spans="1:29" ht="26.25" thickBot="1">
       <c r="A51" s="1"/>
       <c r="B51" s="23" t="s">
         <v>202</v>
@@ -4096,7 +4044,7 @@
       <c r="AB51" s="5"/>
       <c r="AC51" s="5"/>
     </row>
-    <row r="52" spans="1:29" ht="77.25" thickBot="1">
+    <row r="52" spans="1:29" ht="51.75" thickBot="1">
       <c r="A52" s="1"/>
       <c r="B52" s="23" t="s">
         <v>206</v>
@@ -4139,7 +4087,7 @@
       <c r="AB52" s="5"/>
       <c r="AC52" s="5"/>
     </row>
-    <row r="53" spans="1:29" ht="77.25" thickBot="1">
+    <row r="53" spans="1:29" ht="51.75" thickBot="1">
       <c r="A53" s="1"/>
       <c r="B53" s="23" t="s">
         <v>211</v>
@@ -4182,7 +4130,7 @@
       <c r="AB53" s="5"/>
       <c r="AC53" s="5"/>
     </row>
-    <row r="54" spans="1:29" ht="51.75" thickBot="1">
+    <row r="54" spans="1:29" ht="39" thickBot="1">
       <c r="A54" s="1"/>
       <c r="B54" s="23" t="s">
         <v>216</v>
@@ -4225,7 +4173,7 @@
       <c r="AB54" s="5"/>
       <c r="AC54" s="5"/>
     </row>
-    <row r="55" spans="1:29" ht="64.5" thickBot="1">
+    <row r="55" spans="1:29" ht="39" thickBot="1">
       <c r="A55" s="1"/>
       <c r="B55" s="23" t="s">
         <v>221</v>
@@ -4268,7 +4216,7 @@
       <c r="AB55" s="5"/>
       <c r="AC55" s="5"/>
     </row>
-    <row r="56" spans="1:29" ht="77.25" thickBot="1">
+    <row r="56" spans="1:29" ht="51.75" thickBot="1">
       <c r="A56" s="1"/>
       <c r="B56" s="23" t="s">
         <v>225</v>
@@ -4311,7 +4259,7 @@
       <c r="AB56" s="5"/>
       <c r="AC56" s="5"/>
     </row>
-    <row r="57" spans="1:29" ht="64.5" thickBot="1">
+    <row r="57" spans="1:29" ht="51.75" thickBot="1">
       <c r="A57" s="1"/>
       <c r="B57" s="23" t="s">
         <v>228</v>
@@ -4354,7 +4302,7 @@
       <c r="AB57" s="5"/>
       <c r="AC57" s="5"/>
     </row>
-    <row r="58" spans="1:29" ht="51.75" thickBot="1">
+    <row r="58" spans="1:29" ht="39" thickBot="1">
       <c r="A58" s="1"/>
       <c r="B58" s="23" t="s">
         <v>233</v>
@@ -4397,7 +4345,7 @@
       <c r="AB58" s="5"/>
       <c r="AC58" s="5"/>
     </row>
-    <row r="59" spans="1:29" ht="64.5" thickBot="1">
+    <row r="59" spans="1:29" ht="51.75" thickBot="1">
       <c r="A59" s="1"/>
       <c r="B59" s="23" t="s">
         <v>237</v>
@@ -4440,7 +4388,7 @@
       <c r="AB59" s="5"/>
       <c r="AC59" s="5"/>
     </row>
-    <row r="60" spans="1:29" ht="64.5" thickBot="1">
+    <row r="60" spans="1:29" ht="39" thickBot="1">
       <c r="A60" s="1"/>
       <c r="B60" s="23" t="s">
         <v>242</v>
@@ -4483,7 +4431,7 @@
       <c r="AB60" s="5"/>
       <c r="AC60" s="5"/>
     </row>
-    <row r="61" spans="1:29" ht="51.75" thickBot="1">
+    <row r="61" spans="1:29" ht="39" thickBot="1">
       <c r="A61" s="1"/>
       <c r="B61" s="23" t="s">
         <v>247</v>
@@ -4526,7 +4474,7 @@
       <c r="AB61" s="5"/>
       <c r="AC61" s="5"/>
     </row>
-    <row r="62" spans="1:29" ht="90" thickBot="1">
+    <row r="62" spans="1:29" ht="51.75" thickBot="1">
       <c r="A62" s="1"/>
       <c r="B62" s="23" t="s">
         <v>252</v>
@@ -4569,7 +4517,7 @@
       <c r="AB62" s="5"/>
       <c r="AC62" s="5"/>
     </row>
-    <row r="63" spans="1:29" ht="77.25" thickBot="1">
+    <row r="63" spans="1:29" ht="51.75" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="23" t="s">
         <v>257</v>
@@ -4612,7 +4560,7 @@
       <c r="AB63" s="5"/>
       <c r="AC63" s="5"/>
     </row>
-    <row r="64" spans="1:29" ht="64.5" thickBot="1">
+    <row r="64" spans="1:29" ht="39" thickBot="1">
       <c r="A64" s="1"/>
       <c r="B64" s="23" t="s">
         <v>261</v>
@@ -4655,7 +4603,7 @@
       <c r="AB64" s="5"/>
       <c r="AC64" s="5"/>
     </row>
-    <row r="65" spans="1:29" ht="77.25" thickBot="1">
+    <row r="65" spans="1:29" ht="51.75" thickBot="1">
       <c r="A65" s="1"/>
       <c r="B65" s="23" t="s">
         <v>265</v>
@@ -4698,7 +4646,7 @@
       <c r="AB65" s="5"/>
       <c r="AC65" s="5"/>
     </row>
-    <row r="66" spans="1:29" ht="90" thickBot="1">
+    <row r="66" spans="1:29" ht="64.5" thickBot="1">
       <c r="A66" s="1"/>
       <c r="B66" s="23" t="s">
         <v>269</v>
@@ -4741,7 +4689,7 @@
       <c r="AB66" s="5"/>
       <c r="AC66" s="5"/>
     </row>
-    <row r="67" spans="1:29" ht="90" thickBot="1">
+    <row r="67" spans="1:29" ht="51.75" thickBot="1">
       <c r="A67" s="1"/>
       <c r="B67" s="23" t="s">
         <v>273</v>
@@ -4784,7 +4732,7 @@
       <c r="AB67" s="5"/>
       <c r="AC67" s="5"/>
     </row>
-    <row r="68" spans="1:29" ht="64.5" thickBot="1">
+    <row r="68" spans="1:29" ht="51.75" thickBot="1">
       <c r="A68" s="1"/>
       <c r="B68" s="23" t="s">
         <v>277</v>
@@ -4827,7 +4775,7 @@
       <c r="AB68" s="5"/>
       <c r="AC68" s="5"/>
     </row>
-    <row r="69" spans="1:29" ht="77.25" thickBot="1">
+    <row r="69" spans="1:29" ht="51.75" thickBot="1">
       <c r="A69" s="1"/>
       <c r="B69" s="23" t="s">
         <v>281</v>
@@ -4870,7 +4818,7 @@
       <c r="AB69" s="5"/>
       <c r="AC69" s="5"/>
     </row>
-    <row r="70" spans="1:29" ht="64.5" thickBot="1">
+    <row r="70" spans="1:29" ht="39" thickBot="1">
       <c r="A70" s="1"/>
       <c r="B70" s="23" t="s">
         <v>286</v>
@@ -4913,7 +4861,7 @@
       <c r="AB70" s="5"/>
       <c r="AC70" s="5"/>
     </row>
-    <row r="71" spans="1:29" ht="90" thickBot="1">
+    <row r="71" spans="1:29" ht="51.75" thickBot="1">
       <c r="A71" s="1"/>
       <c r="B71" s="23" t="s">
         <v>291</v>
@@ -4956,7 +4904,7 @@
       <c r="AB71" s="5"/>
       <c r="AC71" s="5"/>
     </row>
-    <row r="72" spans="1:29" ht="64.5" thickBot="1">
+    <row r="72" spans="1:29" ht="39" thickBot="1">
       <c r="A72" s="1"/>
       <c r="B72" s="23" t="s">
         <v>296</v>
@@ -4999,7 +4947,7 @@
       <c r="AB72" s="5"/>
       <c r="AC72" s="5"/>
     </row>
-    <row r="73" spans="1:29" ht="64.5" thickBot="1">
+    <row r="73" spans="1:29" ht="51.75" thickBot="1">
       <c r="A73" s="1"/>
       <c r="B73" s="23" t="s">
         <v>300</v>
@@ -5042,7 +4990,7 @@
       <c r="AB73" s="5"/>
       <c r="AC73" s="5"/>
     </row>
-    <row r="74" spans="1:29" ht="77.25" thickBot="1">
+    <row r="74" spans="1:29" ht="51.75" thickBot="1">
       <c r="A74" s="1"/>
       <c r="B74" s="23" t="s">
         <v>304</v>
@@ -5085,7 +5033,7 @@
       <c r="AB74" s="5"/>
       <c r="AC74" s="5"/>
     </row>
-    <row r="75" spans="1:29" ht="39" thickBot="1">
+    <row r="75" spans="1:29" ht="26.25" thickBot="1">
       <c r="A75" s="1"/>
       <c r="B75" s="23" t="s">
         <v>309</v>
@@ -5128,7 +5076,7 @@
       <c r="AB75" s="5"/>
       <c r="AC75" s="5"/>
     </row>
-    <row r="76" spans="1:29" ht="77.25" thickBot="1">
+    <row r="76" spans="1:29" ht="39" thickBot="1">
       <c r="A76" s="1"/>
       <c r="B76" s="23" t="s">
         <v>314</v>
@@ -5171,7 +5119,7 @@
       <c r="AB76" s="5"/>
       <c r="AC76" s="5"/>
     </row>
-    <row r="77" spans="1:29" ht="77.25" thickBot="1">
+    <row r="77" spans="1:29" ht="51.75" thickBot="1">
       <c r="A77" s="1"/>
       <c r="B77" s="23" t="s">
         <v>319</v>
@@ -5214,7 +5162,7 @@
       <c r="AB77" s="5"/>
       <c r="AC77" s="5"/>
     </row>
-    <row r="78" spans="1:29" ht="77.25" thickBot="1">
+    <row r="78" spans="1:29" ht="51.75" thickBot="1">
       <c r="A78" s="1"/>
       <c r="B78" s="23" t="s">
         <v>324</v>
@@ -5257,7 +5205,7 @@
       <c r="AB78" s="5"/>
       <c r="AC78" s="5"/>
     </row>
-    <row r="79" spans="1:29" ht="77.25" thickBot="1">
+    <row r="79" spans="1:29" ht="39" thickBot="1">
       <c r="A79" s="1"/>
       <c r="B79" s="23" t="s">
         <v>329</v>
@@ -5300,7 +5248,7 @@
       <c r="AB79" s="5"/>
       <c r="AC79" s="5"/>
     </row>
-    <row r="80" spans="1:29" ht="51.75" thickBot="1">
+    <row r="80" spans="1:29" ht="39" thickBot="1">
       <c r="A80" s="1"/>
       <c r="B80" s="23" t="s">
         <v>334</v>
@@ -5343,7 +5291,7 @@
       <c r="AB80" s="5"/>
       <c r="AC80" s="5"/>
     </row>
-    <row r="81" spans="1:29" ht="64.5" thickBot="1">
+    <row r="81" spans="1:29" ht="39" thickBot="1">
       <c r="A81" s="1"/>
       <c r="B81" s="23" t="s">
         <v>339</v>
@@ -5386,7 +5334,7 @@
       <c r="AB81" s="5"/>
       <c r="AC81" s="5"/>
     </row>
-    <row r="82" spans="1:29" ht="90" thickBot="1">
+    <row r="82" spans="1:29" ht="51.75" thickBot="1">
       <c r="A82" s="1"/>
       <c r="B82" s="23" t="s">
         <v>344</v>
@@ -5429,7 +5377,7 @@
       <c r="AB82" s="5"/>
       <c r="AC82" s="5"/>
     </row>
-    <row r="83" spans="1:29" ht="77.25" thickBot="1">
+    <row r="83" spans="1:29" ht="51.75" thickBot="1">
       <c r="A83" s="1"/>
       <c r="B83" s="23" t="s">
         <v>348</v>
@@ -5472,7 +5420,7 @@
       <c r="AB83" s="5"/>
       <c r="AC83" s="5"/>
     </row>
-    <row r="84" spans="1:29" ht="90" thickBot="1">
+    <row r="84" spans="1:29" ht="51.75" thickBot="1">
       <c r="A84" s="1"/>
       <c r="B84" s="23" t="s">
         <v>353</v>
@@ -5515,7 +5463,7 @@
       <c r="AB84" s="5"/>
       <c r="AC84" s="5"/>
     </row>
-    <row r="85" spans="1:29" ht="77.25" thickBot="1">
+    <row r="85" spans="1:29" ht="39" thickBot="1">
       <c r="A85" s="1"/>
       <c r="B85" s="23" t="s">
         <v>357</v>
@@ -5558,7 +5506,7 @@
       <c r="AB85" s="5"/>
       <c r="AC85" s="5"/>
     </row>
-    <row r="86" spans="1:29" ht="64.5" thickBot="1">
+    <row r="86" spans="1:29" ht="39" thickBot="1">
       <c r="A86" s="1"/>
       <c r="B86" s="23" t="s">
         <v>361</v>
@@ -5601,7 +5549,7 @@
       <c r="AB86" s="5"/>
       <c r="AC86" s="5"/>
     </row>
-    <row r="87" spans="1:29" ht="51.75" thickBot="1">
+    <row r="87" spans="1:29" ht="26.25" thickBot="1">
       <c r="A87" s="1"/>
       <c r="B87" s="23" t="s">
         <v>366</v>
@@ -5644,7 +5592,7 @@
       <c r="AB87" s="5"/>
       <c r="AC87" s="5"/>
     </row>
-    <row r="88" spans="1:29" ht="64.5" thickBot="1">
+    <row r="88" spans="1:29" ht="39" thickBot="1">
       <c r="A88" s="1"/>
       <c r="B88" s="23" t="s">
         <v>370</v>
@@ -5687,7 +5635,7 @@
       <c r="AB88" s="5"/>
       <c r="AC88" s="5"/>
     </row>
-    <row r="89" spans="1:29" ht="51.75" thickBot="1">
+    <row r="89" spans="1:29" ht="26.25" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="23" t="s">
         <v>375</v>
@@ -5730,7 +5678,7 @@
       <c r="AB89" s="5"/>
       <c r="AC89" s="5"/>
     </row>
-    <row r="90" spans="1:29" ht="64.5" thickBot="1">
+    <row r="90" spans="1:29" ht="39" thickBot="1">
       <c r="A90" s="1"/>
       <c r="B90" s="23" t="s">
         <v>379</v>
@@ -5773,7 +5721,7 @@
       <c r="AB90" s="5"/>
       <c r="AC90" s="5"/>
     </row>
-    <row r="91" spans="1:29" ht="51.75" thickBot="1">
+    <row r="91" spans="1:29" ht="26.25" thickBot="1">
       <c r="A91" s="1"/>
       <c r="B91" s="23" t="s">
         <v>382</v>
@@ -5816,7 +5764,7 @@
       <c r="AB91" s="5"/>
       <c r="AC91" s="5"/>
     </row>
-    <row r="92" spans="1:29" ht="77.25" thickBot="1">
+    <row r="92" spans="1:29" ht="51.75" thickBot="1">
       <c r="A92" s="1"/>
       <c r="B92" s="23" t="s">
         <v>385</v>
@@ -5859,7 +5807,7 @@
       <c r="AB92" s="5"/>
       <c r="AC92" s="5"/>
     </row>
-    <row r="93" spans="1:29" ht="64.5" thickBot="1">
+    <row r="93" spans="1:29" ht="39" thickBot="1">
       <c r="A93" s="1"/>
       <c r="B93" s="23" t="s">
         <v>390</v>
@@ -5902,7 +5850,7 @@
       <c r="AB93" s="5"/>
       <c r="AC93" s="5"/>
     </row>
-    <row r="94" spans="1:29" ht="64.5" thickBot="1">
+    <row r="94" spans="1:29" ht="39" thickBot="1">
       <c r="A94" s="1"/>
       <c r="B94" s="23" t="s">
         <v>393</v>
@@ -5945,7 +5893,7 @@
       <c r="AB94" s="5"/>
       <c r="AC94" s="5"/>
     </row>
-    <row r="95" spans="1:29" ht="64.5" thickBot="1">
+    <row r="95" spans="1:29" ht="39" thickBot="1">
       <c r="A95" s="1"/>
       <c r="B95" s="23" t="s">
         <v>396</v>
@@ -5988,7 +5936,7 @@
       <c r="AB95" s="5"/>
       <c r="AC95" s="5"/>
     </row>
-    <row r="96" spans="1:29" ht="64.5" thickBot="1">
+    <row r="96" spans="1:29" ht="39" thickBot="1">
       <c r="A96" s="1"/>
       <c r="B96" s="23" t="s">
         <v>399</v>
@@ -6031,7 +5979,7 @@
       <c r="AB96" s="5"/>
       <c r="AC96" s="5"/>
     </row>
-    <row r="97" spans="1:29" ht="64.5" thickBot="1">
+    <row r="97" spans="1:29" ht="39" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="23" t="s">
         <v>402</v>
@@ -6074,7 +6022,7 @@
       <c r="AB97" s="5"/>
       <c r="AC97" s="5"/>
     </row>
-    <row r="98" spans="1:29" ht="64.5" thickBot="1">
+    <row r="98" spans="1:29" ht="39" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="23" t="s">
         <v>405</v>
@@ -6117,7 +6065,7 @@
       <c r="AB98" s="5"/>
       <c r="AC98" s="5"/>
     </row>
-    <row r="99" spans="1:29" ht="64.5" thickBot="1">
+    <row r="99" spans="1:29" ht="39" thickBot="1">
       <c r="A99" s="1"/>
       <c r="B99" s="23" t="s">
         <v>408</v>
@@ -6160,7 +6108,7 @@
       <c r="AB99" s="5"/>
       <c r="AC99" s="5"/>
     </row>
-    <row r="100" spans="1:29" ht="64.5" thickBot="1">
+    <row r="100" spans="1:29" ht="39" thickBot="1">
       <c r="A100" s="1"/>
       <c r="B100" s="23" t="s">
         <v>411</v>
@@ -6203,7 +6151,7 @@
       <c r="AB100" s="5"/>
       <c r="AC100" s="5"/>
     </row>
-    <row r="101" spans="1:29" ht="90" thickBot="1">
+    <row r="101" spans="1:29" ht="64.5" thickBot="1">
       <c r="A101" s="1"/>
       <c r="B101" s="23" t="s">
         <v>414</v>
@@ -6246,7 +6194,7 @@
       <c r="AB101" s="5"/>
       <c r="AC101" s="5"/>
     </row>
-    <row r="102" spans="1:29" ht="39" thickBot="1">
+    <row r="102" spans="1:29" ht="26.25" thickBot="1">
       <c r="A102" s="1"/>
       <c r="B102" s="23" t="s">
         <v>419</v>
@@ -6289,7 +6237,7 @@
       <c r="AB102" s="5"/>
       <c r="AC102" s="5"/>
     </row>
-    <row r="103" spans="1:29" ht="51.75" thickBot="1">
+    <row r="103" spans="1:29" ht="39" thickBot="1">
       <c r="A103" s="1"/>
       <c r="B103" s="23" t="s">
         <v>424</v>
@@ -6332,7 +6280,7 @@
       <c r="AB103" s="5"/>
       <c r="AC103" s="5"/>
     </row>
-    <row r="104" spans="1:29" ht="64.5" thickBot="1">
+    <row r="104" spans="1:29" ht="39" thickBot="1">
       <c r="A104" s="1"/>
       <c r="B104" s="23" t="s">
         <v>428</v>
@@ -6375,7 +6323,7 @@
       <c r="AB104" s="5"/>
       <c r="AC104" s="5"/>
     </row>
-    <row r="105" spans="1:29" ht="39" thickBot="1">
+    <row r="105" spans="1:29" ht="26.25" thickBot="1">
       <c r="A105" s="1"/>
       <c r="B105" s="23" t="s">
         <v>433</v>
@@ -6418,7 +6366,7 @@
       <c r="AB105" s="5"/>
       <c r="AC105" s="5"/>
     </row>
-    <row r="106" spans="1:29" ht="39" thickBot="1">
+    <row r="106" spans="1:29" ht="26.25" thickBot="1">
       <c r="A106" s="1"/>
       <c r="B106" s="23" t="s">
         <v>438</v>
@@ -6461,7 +6409,7 @@
       <c r="AB106" s="5"/>
       <c r="AC106" s="5"/>
     </row>
-    <row r="107" spans="1:29" ht="64.5" thickBot="1">
+    <row r="107" spans="1:29" ht="51.75" thickBot="1">
       <c r="A107" s="1"/>
       <c r="B107" s="23" t="s">
         <v>443</v>
@@ -6473,10 +6421,10 @@
         <v>445</v>
       </c>
       <c r="E107" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="F107" s="24" t="s">
         <v>446</v>
-      </c>
-      <c r="F107" s="24" t="s">
-        <v>447</v>
       </c>
       <c r="G107" s="24"/>
       <c r="H107" s="24" t="s">
@@ -6504,32 +6452,20 @@
       <c r="AB107" s="5"/>
       <c r="AC107" s="5"/>
     </row>
-    <row r="108" spans="1:29" ht="64.5" thickBot="1">
+    <row r="108" spans="1:29" ht="18">
       <c r="A108" s="1"/>
-      <c r="B108" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>449</v>
-      </c>
-      <c r="D108" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="E108" s="24" t="s">
-        <v>451</v>
-      </c>
-      <c r="F108" s="24" t="s">
-        <v>452</v>
-      </c>
-      <c r="G108" s="24"/>
-      <c r="H108" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I108" s="24"/>
-      <c r="J108" s="24"/>
-      <c r="K108" s="24"/>
-      <c r="L108" s="24"/>
-      <c r="M108" s="24"/>
+      <c r="B108" s="22"/>
+      <c r="C108" s="22"/>
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="22"/>
+      <c r="H108" s="22"/>
+      <c r="I108" s="22"/>
+      <c r="J108" s="22"/>
+      <c r="K108" s="22"/>
+      <c r="L108" s="22"/>
+      <c r="M108" s="22"/>
       <c r="N108" s="5"/>
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
@@ -6547,32 +6483,20 @@
       <c r="AB108" s="5"/>
       <c r="AC108" s="5"/>
     </row>
-    <row r="109" spans="1:29" ht="77.25" thickBot="1">
+    <row r="109" spans="1:29" ht="18">
       <c r="A109" s="1"/>
-      <c r="B109" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="C109" s="24" t="s">
-        <v>454</v>
-      </c>
-      <c r="D109" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="E109" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="F109" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="G109" s="24"/>
-      <c r="H109" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I109" s="24"/>
-      <c r="J109" s="24"/>
-      <c r="K109" s="24"/>
-      <c r="L109" s="24"/>
-      <c r="M109" s="24"/>
+      <c r="B109" s="22"/>
+      <c r="C109" s="22"/>
+      <c r="D109" s="22"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="22"/>
+      <c r="G109" s="22"/>
+      <c r="H109" s="22"/>
+      <c r="I109" s="22"/>
+      <c r="J109" s="22"/>
+      <c r="K109" s="22"/>
+      <c r="L109" s="22"/>
+      <c r="M109" s="22"/>
       <c r="N109" s="5"/>
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
@@ -6590,32 +6514,20 @@
       <c r="AB109" s="5"/>
       <c r="AC109" s="5"/>
     </row>
-    <row r="110" spans="1:29" ht="77.25" thickBot="1">
+    <row r="110" spans="1:29" ht="18">
       <c r="A110" s="1"/>
-      <c r="B110" s="23" t="s">
-        <v>457</v>
-      </c>
-      <c r="C110" s="24" t="s">
-        <v>458</v>
-      </c>
-      <c r="D110" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="E110" s="24" t="s">
-        <v>460</v>
-      </c>
-      <c r="F110" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="G110" s="24"/>
-      <c r="H110" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I110" s="24"/>
-      <c r="J110" s="24"/>
-      <c r="K110" s="24"/>
-      <c r="L110" s="24"/>
-      <c r="M110" s="24"/>
+      <c r="B110" s="22"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22"/>
+      <c r="G110" s="22"/>
+      <c r="H110" s="22"/>
+      <c r="I110" s="22"/>
+      <c r="J110" s="22"/>
+      <c r="K110" s="22"/>
+      <c r="L110" s="22"/>
+      <c r="M110" s="22"/>
       <c r="N110" s="5"/>
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
@@ -6633,32 +6545,20 @@
       <c r="AB110" s="5"/>
       <c r="AC110" s="5"/>
     </row>
-    <row r="111" spans="1:29" ht="90" thickBot="1">
+    <row r="111" spans="1:29" ht="18">
       <c r="A111" s="1"/>
-      <c r="B111" s="23" t="s">
-        <v>462</v>
-      </c>
-      <c r="C111" s="24" t="s">
-        <v>463</v>
-      </c>
-      <c r="D111" s="24" t="s">
-        <v>464</v>
-      </c>
-      <c r="E111" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="F111" s="24" t="s">
-        <v>465</v>
-      </c>
-      <c r="G111" s="24"/>
-      <c r="H111" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I111" s="24"/>
-      <c r="J111" s="24"/>
-      <c r="K111" s="24"/>
-      <c r="L111" s="24"/>
-      <c r="M111" s="24"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
+      <c r="G111" s="22"/>
+      <c r="H111" s="22"/>
+      <c r="I111" s="22"/>
+      <c r="J111" s="22"/>
+      <c r="K111" s="22"/>
+      <c r="L111" s="22"/>
+      <c r="M111" s="22"/>
       <c r="N111" s="5"/>
       <c r="O111" s="5"/>
       <c r="P111" s="5"/>
@@ -34235,132 +34135,9 @@
       <c r="AB1000" s="5"/>
       <c r="AC1000" s="5"/>
     </row>
-    <row r="1001" spans="1:29" ht="18">
-      <c r="A1001" s="1"/>
-      <c r="B1001" s="22"/>
-      <c r="C1001" s="22"/>
-      <c r="D1001" s="22"/>
-      <c r="E1001" s="22"/>
-      <c r="F1001" s="22"/>
-      <c r="G1001" s="22"/>
-      <c r="H1001" s="22"/>
-      <c r="I1001" s="22"/>
-      <c r="J1001" s="22"/>
-      <c r="K1001" s="22"/>
-      <c r="L1001" s="22"/>
-      <c r="M1001" s="22"/>
-      <c r="N1001" s="5"/>
-      <c r="O1001" s="5"/>
-      <c r="P1001" s="5"/>
-      <c r="Q1001" s="5"/>
-      <c r="R1001" s="5"/>
-      <c r="S1001" s="5"/>
-      <c r="T1001" s="5"/>
-      <c r="U1001" s="5"/>
-      <c r="V1001" s="5"/>
-      <c r="W1001" s="5"/>
-      <c r="X1001" s="5"/>
-      <c r="Y1001" s="5"/>
-      <c r="Z1001" s="5"/>
-      <c r="AA1001" s="5"/>
-      <c r="AB1001" s="5"/>
-      <c r="AC1001" s="5"/>
-    </row>
-    <row r="1002" spans="1:29" ht="18">
-      <c r="A1002" s="1"/>
-      <c r="B1002" s="22"/>
-      <c r="C1002" s="22"/>
-      <c r="D1002" s="22"/>
-      <c r="E1002" s="22"/>
-      <c r="F1002" s="22"/>
-      <c r="G1002" s="22"/>
-      <c r="H1002" s="22"/>
-      <c r="I1002" s="22"/>
-      <c r="J1002" s="22"/>
-      <c r="K1002" s="22"/>
-      <c r="L1002" s="22"/>
-      <c r="M1002" s="22"/>
-      <c r="N1002" s="5"/>
-      <c r="O1002" s="5"/>
-      <c r="P1002" s="5"/>
-      <c r="Q1002" s="5"/>
-      <c r="R1002" s="5"/>
-      <c r="S1002" s="5"/>
-      <c r="T1002" s="5"/>
-      <c r="U1002" s="5"/>
-      <c r="V1002" s="5"/>
-      <c r="W1002" s="5"/>
-      <c r="X1002" s="5"/>
-      <c r="Y1002" s="5"/>
-      <c r="Z1002" s="5"/>
-      <c r="AA1002" s="5"/>
-      <c r="AB1002" s="5"/>
-      <c r="AC1002" s="5"/>
-    </row>
-    <row r="1003" spans="1:29" ht="18">
-      <c r="A1003" s="1"/>
-      <c r="B1003" s="22"/>
-      <c r="C1003" s="22"/>
-      <c r="D1003" s="22"/>
-      <c r="E1003" s="22"/>
-      <c r="F1003" s="22"/>
-      <c r="G1003" s="22"/>
-      <c r="H1003" s="22"/>
-      <c r="I1003" s="22"/>
-      <c r="J1003" s="22"/>
-      <c r="K1003" s="22"/>
-      <c r="L1003" s="22"/>
-      <c r="M1003" s="22"/>
-      <c r="N1003" s="5"/>
-      <c r="O1003" s="5"/>
-      <c r="P1003" s="5"/>
-      <c r="Q1003" s="5"/>
-      <c r="R1003" s="5"/>
-      <c r="S1003" s="5"/>
-      <c r="T1003" s="5"/>
-      <c r="U1003" s="5"/>
-      <c r="V1003" s="5"/>
-      <c r="W1003" s="5"/>
-      <c r="X1003" s="5"/>
-      <c r="Y1003" s="5"/>
-      <c r="Z1003" s="5"/>
-      <c r="AA1003" s="5"/>
-      <c r="AB1003" s="5"/>
-      <c r="AC1003" s="5"/>
-    </row>
-    <row r="1004" spans="1:29" ht="18">
-      <c r="A1004" s="1"/>
-      <c r="B1004" s="22"/>
-      <c r="C1004" s="22"/>
-      <c r="D1004" s="22"/>
-      <c r="E1004" s="22"/>
-      <c r="F1004" s="22"/>
-      <c r="G1004" s="22"/>
-      <c r="H1004" s="22"/>
-      <c r="I1004" s="22"/>
-      <c r="J1004" s="22"/>
-      <c r="K1004" s="22"/>
-      <c r="L1004" s="22"/>
-      <c r="M1004" s="22"/>
-      <c r="N1004" s="5"/>
-      <c r="O1004" s="5"/>
-      <c r="P1004" s="5"/>
-      <c r="Q1004" s="5"/>
-      <c r="R1004" s="5"/>
-      <c r="S1004" s="5"/>
-      <c r="T1004" s="5"/>
-      <c r="U1004" s="5"/>
-      <c r="V1004" s="5"/>
-      <c r="W1004" s="5"/>
-      <c r="X1004" s="5"/>
-      <c r="Y1004" s="5"/>
-      <c r="Z1004" s="5"/>
-      <c r="AA1004" s="5"/>
-      <c r="AB1004" s="5"/>
-      <c r="AC1004" s="5"/>
-    </row>
   </sheetData>
   <autoFilter ref="B10:M12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"High,Medium,Low"</formula1>
